--- a/estadisticas/arch/dtrp30.xlsx
+++ b/estadisticas/arch/dtrp30.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/proyectos/SuperIntendenciaNacionalSalud/Argo/src/2/estadisticas/arch/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATOS-EXT/proyectos/Gestor documental Universidad Militar/ArgoUMNG/src/2/estadisticas/arch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15AE452-5EE2-1645-A7F8-F0AEF9F55096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A9C5F7-9E77-CB49-ACDF-27516CD3D34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4360" yWindow="760" windowWidth="25900" windowHeight="15160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -504,43 +504,44 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>237960</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>368116</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>128840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2275920</xdr:colOff>
+      <xdr:colOff>1106942</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>92880</xdr:rowOff>
+      <xdr:rowOff>144117</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1" descr="Logo SuperArgo">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8826DE91-9A79-FB4E-8968-98C8CDD5ADBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="783720" y="0"/>
-          <a:ext cx="3524040" cy="816480"/>
+          <a:off x="2107464" y="128840"/>
+          <a:ext cx="738826" cy="723900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
